--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:45:11+00:00</t>
+    <t>2025-07-08T14:52:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -946,7 +946,7 @@
     <t>Classification of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode|3.0.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -1166,7 +1166,7 @@
     <t>Indicates the urgency of the encounter.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActPriority|3.0.0</t>
   </si>
   <si>
     <t>.priorityCode</t>
@@ -1185,7 +1185,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|Group)
 </t>
   </si>
   <si>

--- a/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-encounter.xlsx
+++ b/nr-update-practitioner-qualification-reslice/ig/StructureDefinition-fr-core-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T14:52:18+00:00</t>
+    <t>2025-07-10T12:55:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
